--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -49,6 +49,9 @@
     <x:t>Spanish</x:t>
   </x:si>
   <x:si>
+    <x:t>Bug Status</x:t>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
@@ -73,6 +76,9 @@
     <x:t>Not Affected</x:t>
   </x:si>
   <x:si>
+    <x:t>Uploaded</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -85,6 +91,9 @@
     <x:t>ggggg</x:t>
   </x:si>
   <x:si>
+    <x:t>Reporting</x:t>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
@@ -97,6 +106,9 @@
     <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
   </x:si>
   <x:si>
+    <x:t>Ready To Vet</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
@@ -107,6 +119,42 @@
   </x:si>
   <x:si>
     <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Inconsistent Translation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shortening</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdhhdhdh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fjfgjgjsgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sjfgjgjgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duplicate</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -457,22 +505,21 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K5"/>
+  <x:dimension ref="A1:L8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="110.996339" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="45.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="48.139196" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="10" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="49.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="11" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:11">
+    <x:row r="1" spans="1:12" ht="12" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -506,145 +553,274 @@
       <x:c r="K1" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="L1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:11">
+    <x:row r="2" spans="1:12" ht="12" customHeight="1">
       <x:c r="A2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A3" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="E3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:11">
-      <x:c r="A3" s="0" t="s">
+    <x:row r="4" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="J4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="C5" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="D5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
     </x:row>
-    <x:row r="4" spans="1:11">
-      <x:c r="A4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
+    <x:row r="8" spans="1:12" ht="12" customHeight="1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="C8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:11">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="D8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="H8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -128,6 +128,9 @@
   </x:si>
   <x:si>
     <x:t>Inconsistent Translation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[IT, DE, ES]</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -723,7 +726,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>34</x:v>
@@ -732,7 +735,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>18</x:v>
@@ -749,7 +752,7 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12" customHeight="1">
       <x:c r="A7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>13</x:v>
@@ -758,16 +761,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>19</x:v>
@@ -787,7 +790,7 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12" customHeight="1">
       <x:c r="A8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
@@ -796,13 +799,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>27</x:v>
@@ -820,7 +823,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -52,6 +52,30 @@
     <x:t>Bug Status</x:t>
   </x:si>
   <x:si>
+    <x:t>French Observed Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>French Expected Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Italian Observed Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Italian Expected Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>German Observed Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>German Expected Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spanish Observed Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spanish Expected Result</x:t>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
@@ -64,7 +88,7 @@
     <x:t>Compliance</x:t>
   </x:si>
   <x:si>
-    <x:t>SSS</x:t>
+    <x:t>[FR, ES] SSS</x:t>
   </x:si>
   <x:si>
     <x:t>SSSS</x:t>
@@ -79,6 +103,15 @@
     <x:t>Uploaded</x:t>
   </x:si>
   <x:si>
+    <x:t>AAAA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBBB</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -116,9 +149,6 @@
   </x:si>
   <x:si>
     <x:t>WWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>Approved</x:t>
@@ -508,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:L8"/>
+  <x:dimension ref="A1:T8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
@@ -520,9 +550,16 @@
     <x:col min="7" max="7" width="49.996339" style="0" customWidth="1"/>
     <x:col min="8" max="11" width="11.853482" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22.424911" style="0" customWidth="1"/>
+    <x:col min="14" max="15" width="21.567768" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20.996339" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="23.424911" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="22.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="23.282054" style="0" customWidth="1"/>
+    <x:col min="20" max="20" width="22.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:12" ht="12" customHeight="1">
+    <x:row r="1" spans="1:20" ht="14.25" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -559,271 +596,463 @@
       <x:c r="L1" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N1" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O1" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P1" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q1" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R1" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="S1" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="T1" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:12" ht="12" customHeight="1">
+    <x:row r="2" spans="1:20" ht="14.25" customHeight="1">
       <x:c r="A2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:12" ht="12" customHeight="1">
+    <x:row r="3" spans="1:20" ht="14.25" customHeight="1">
       <x:c r="A3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:20" ht="14.25" customHeight="1">
+      <x:c r="A4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>25</x:v>
+      <x:c r="E4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:12" ht="12" customHeight="1">
-      <x:c r="A4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
+    <x:row r="5" spans="1:20" ht="14.25" customHeight="1">
+      <x:c r="A5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:20" ht="14.25" customHeight="1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="I6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:20" ht="14.25" customHeight="1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>30</x:v>
+      <x:c r="M7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T7" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:12" ht="12" customHeight="1">
-      <x:c r="A5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:12" ht="12" customHeight="1">
-      <x:c r="A6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
+    <x:row r="8" spans="1:20" ht="14.25" customHeight="1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:12" ht="12" customHeight="1">
-      <x:c r="A7" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:12" ht="12" customHeight="1">
-      <x:c r="A8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="H8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="T8" s="0" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -76,6 +76,15 @@
     <x:t>Spanish Expected Result</x:t>
   </x:si>
   <x:si>
+    <x:t>Observed Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Expected Result</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Needs Language Specific Results</x:t>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
@@ -106,12 +115,12 @@
     <x:t>AAAA</x:t>
   </x:si>
   <x:si>
-    <x:t>BBBB</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -140,6 +149,9 @@
   </x:si>
   <x:si>
     <x:t>Ready To Vet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ghjgjghjgj</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -538,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:T8"/>
+  <x:dimension ref="A1:W8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
@@ -557,9 +569,12 @@
     <x:col min="18" max="18" width="22.853482" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="23.282054" style="0" customWidth="1"/>
     <x:col min="20" max="20" width="22.710625" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="15.567768" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="29.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:20" ht="14.25" customHeight="1">
+    <x:row r="1" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -620,439 +635,511 @@
       <x:c r="T1" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="U1" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="V1" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="W1" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:20" ht="14.25" customHeight="1">
+    <x:row r="2" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A2" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="D3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
+      <x:c r="E5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O2" s="0" t="s">
+      <x:c r="I6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T2" s="0" t="s">
-        <x:v>31</x:v>
+      <x:c r="M7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W7" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
+    <x:row r="8" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A5" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A6" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A7" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="Q7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="R7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:20" ht="14.25" customHeight="1">
-      <x:c r="A8" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="Q8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="T8" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W8" s="0" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -97,7 +97,7 @@
     <x:t>Compliance</x:t>
   </x:si>
   <x:si>
-    <x:t>[FR, ES] SSS</x:t>
+    <x:t>[FR, DE, ES] SSS</x:t>
   </x:si>
   <x:si>
     <x:t>SSSS</x:t>
@@ -124,7 +124,7 @@
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>hhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhh</x:t>
+    <x:t>[FR, DE, ES] hhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhh</x:t>
   </x:si>
   <x:si>
     <x:t>dfgdfgd</x:t>
@@ -139,64 +139,67 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
+    <x:t>[FR, IT, DE, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ready To Vet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ghjgjghjgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Inconsistent Translation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[IT, DE, ES]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shortening</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdhhdhdh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fjfgjgjsgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sjfgjgjgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
     <x:t>WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ready To Vet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ghjgjghjgj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Inconsistent Translation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[IT, DE, ES]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shortening</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdhhdhdh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fjfgjgjsgj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sjfgjgjgj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWW</x:t>
   </x:si>
   <x:si>
     <x:t>Duplicate</x:t>
@@ -557,10 +560,12 @@
     <x:col min="2" max="2" width="9.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.996339" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="22.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="110.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="121.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="45.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="49.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="11" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="8" max="9" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.853482" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="22.424911" style="0" customWidth="1"/>
     <x:col min="14" max="15" width="21.567768" style="0" customWidth="1"/>
@@ -674,7 +679,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>29</x:v>
@@ -810,16 +815,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>44</x:v>
@@ -1091,7 +1096,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>29</x:v>
@@ -1106,7 +1111,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>33</x:v>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -97,18 +97,18 @@
     <x:t>Compliance</x:t>
   </x:si>
   <x:si>
-    <x:t>[FR, DE, ES] SSS</x:t>
+    <x:t>[DE, ES] SSS</x:t>
   </x:si>
   <x:si>
     <x:t>SSSS</x:t>
   </x:si>
   <x:si>
+    <x:t>Not Affected</x:t>
+  </x:si>
+  <x:si>
     <x:t>Affected</x:t>
   </x:si>
   <x:si>
-    <x:t>Not Affected</x:t>
-  </x:si>
-  <x:si>
     <x:t>Uploaded</x:t>
   </x:si>
   <x:si>
@@ -118,46 +118,46 @@
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[FR, DE, ES] hhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dfgdfgd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ggggg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reporting</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[FR, IT, DE, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ready To Vet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ghjgjghjgj</x:t>
+  </x:si>
+  <x:si>
     <x:t>Yes</x:t>
   </x:si>
   <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[FR, DE, ES] hhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dfgdfgd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ggggg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Reporting</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[FR, IT, DE, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ready To Vet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ghjgjghjgj</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>WWWWWWWWW</x:t>
+    <x:t>[FR, IT, ES] WWWWWWWWW</x:t>
   </x:si>
   <x:si>
     <x:t>WWWWWWW</x:t>
@@ -172,7 +172,7 @@
     <x:t>Inconsistent Translation</x:t>
   </x:si>
   <x:si>
-    <x:t>[IT, DE, ES]</x:t>
+    <x:t>[FR, DE, ES]</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -193,7 +193,7 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>WWWWWWWWWWWWWWW</x:t>
+    <x:t>[ES] WWWWWWWWWWWWWWW</x:t>
   </x:si>
   <x:si>
     <x:t>WWWWWWWWWWWWWWWWWWWW</x:t>
@@ -203,6 +203,18 @@
   </x:si>
   <x:si>
     <x:t>Duplicate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026/08/05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[FR, IT] FFFFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FFFFFF</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -553,7 +565,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W8"/>
+  <x:dimension ref="A1:W9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
@@ -563,9 +575,7 @@
     <x:col min="5" max="5" width="121.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="45.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="49.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="9" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8.282054" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="8" max="11" width="11.853482" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="12.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="22.424911" style="0" customWidth="1"/>
     <x:col min="14" max="15" width="21.567768" style="0" customWidth="1"/>
@@ -676,13 +686,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>31</x:v>
@@ -718,12 +728,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>24</x:v>
@@ -735,28 +745,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="G3" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="H3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>33</x:v>
@@ -794,7 +804,7 @@
     </x:row>
     <x:row r="4" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -806,61 +816,61 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="G4" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
+      <x:c r="M4" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="M4" s="0" t="s">
+      <x:c r="N4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="W4" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23" ht="14.25" customHeight="1">
@@ -886,16 +896,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>49</x:v>
@@ -963,13 +973,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>33</x:v>
@@ -1028,16 +1038,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>31</x:v>
@@ -1144,6 +1154,77 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A9" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -118,6 +118,9 @@
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>AAAAA</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
@@ -133,10 +136,13 @@
     <x:t>Reporting</x:t>
   </x:si>
   <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>[FR, IT, DE, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+    <x:t>[IT, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
   </x:si>
   <x:si>
     <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
@@ -151,7 +157,7 @@
     <x:t>ghjgjghjgj</x:t>
   </x:si>
   <x:si>
-    <x:t>Yes</x:t>
+    <x:t>fggffgfgf</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -215,6 +221,15 @@
   </x:si>
   <x:si>
     <x:t>FFFFFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[IT, DE, ES] ggggg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gdgdhfhdh</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -565,7 +580,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W9"/>
+  <x:dimension ref="A1:W10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
@@ -710,16 +725,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="Q2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="T2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
         <x:v>33</x:v>
@@ -733,7 +748,7 @@
     </x:row>
     <x:row r="3" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>24</x:v>
@@ -745,13 +760,13 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>30</x:v>
@@ -766,7 +781,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>33</x:v>
@@ -799,12 +814,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -816,66 +831,66 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="S4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="T4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="W4" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>24</x:v>
@@ -887,10 +902,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>33</x:v>
@@ -908,7 +923,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
         <x:v>33</x:v>
@@ -941,12 +956,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>24</x:v>
@@ -955,10 +970,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>33</x:v>
@@ -979,7 +994,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>33</x:v>
@@ -1017,7 +1032,7 @@
     </x:row>
     <x:row r="7" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
@@ -1026,16 +1041,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>29</x:v>
@@ -1088,7 +1103,7 @@
     </x:row>
     <x:row r="8" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>24</x:v>
@@ -1097,16 +1112,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>29</x:v>
@@ -1121,7 +1136,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>33</x:v>
@@ -1159,72 +1174,143 @@
     </x:row>
     <x:row r="9" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A9" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W9" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="S9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="T9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="U9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="W9" s="0" t="s">
+      <x:c r="D10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V10" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W10" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>

--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -133,52 +133,52 @@
     <x:t>ggggg</x:t>
   </x:si>
   <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[IT, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ready To Vet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ghjgjghjgj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fggffgfgf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[FR, IT, ES] WWWWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWWWWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Inconsistent Translation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[FR, DE, ES]</x:t>
+  </x:si>
+  <x:si>
     <x:t>Reporting</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[IT, ES] WWWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ready To Vet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ghjgjghjgj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fggffgfgf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[FR, IT, ES] WWWWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WWWWWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Inconsistent Translation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[FR, DE, ES]</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -781,7 +781,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>33</x:v>
@@ -814,12 +814,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>24</x:v>
@@ -831,38 +831,38 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="M4" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
+      <x:c r="N4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="P4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
@@ -885,12 +885,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>24</x:v>
@@ -902,66 +902,66 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="M5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="N5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="O5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="S5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="U5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V5" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="W5" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>24</x:v>
@@ -970,31 +970,31 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>33</x:v>
@@ -1183,7 +1183,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>67</x:v>
